--- a/tests/testdata/excel/基本.xlsx
+++ b/tests/testdata/excel/基本.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\test\AppData\Local\Temp\win_grep_testdata\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{2D9800B2-A593-40C2-A3C2-9E39272F619B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{F3C21140-1D94-4464-83EF-7C71E0D7118E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3120" yWindow="3120" windowWidth="21600" windowHeight="10515" xr2:uid="{2B83443D-E3EF-4A4C-8088-0CAC1B04BB60}"/>
+    <workbookView xWindow="3120" yWindow="3120" windowWidth="21600" windowHeight="10515" xr2:uid="{6A0B83D6-2134-41A6-8A80-AE531F49DEA4}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -594,7 +594,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E57C74BD-7993-4C06-8B6A-D91EE7DAAC26}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AFF5AB47-FCBB-4D3B-9103-EF3F86479A2C}">
   <dimension ref="A1:G7"/>
   <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
   <sheetData>
@@ -757,7 +757,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A7CE3588-CE7E-4AA9-88F6-923F423BA4D6}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{787D0C07-8F8F-4109-9AD9-092C3A4C72F7}">
   <dimension ref="A1:E13"/>
   <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
   <cols>
@@ -992,7 +992,7 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{42DC38B4-2FD4-420B-A714-66942C846DC1}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{70B413C9-8635-4EE6-B2A1-651FDD01D4BB}">
   <dimension ref="A1:D3"/>
   <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
   <sheetData>
